--- a/src/data/elforbruk/data.xlsx
+++ b/src/data/elforbruk/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magne.syljuasen\kode\Kolbotn\src\data\elforbruk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D50E0F9-845C-4967-9D7A-99026642CC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563F358D-E46D-4A8C-99DA-C177993FD4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24705" yWindow="2280" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="640">
   <si>
     <t>dato</t>
   </si>
@@ -1954,9 +1954,6 @@
   </si>
   <si>
     <t>18.11.2025</t>
-  </si>
-  <si>
-    <t>sdds</t>
   </si>
 </sst>
 </file>
@@ -7120,7 +7117,7 @@
         <v>236.65</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>593</v>
       </c>
@@ -7128,7 +7125,7 @@
         <v>236.55</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>594</v>
       </c>
@@ -7136,7 +7133,7 @@
         <v>236.7</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>595</v>
       </c>
@@ -7144,7 +7141,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>596</v>
       </c>
@@ -7152,7 +7149,7 @@
         <v>411.05</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>597</v>
       </c>
@@ -7160,7 +7157,7 @@
         <v>489.8</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>598</v>
       </c>
@@ -7168,7 +7165,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>599</v>
       </c>
@@ -7176,7 +7173,7 @@
         <v>235.85</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>600</v>
       </c>
@@ -7184,7 +7181,7 @@
         <v>235.95</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>601</v>
       </c>
@@ -7192,7 +7189,7 @@
         <v>236.05</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>602</v>
       </c>
@@ -7200,7 +7197,7 @@
         <v>236.1</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>603</v>
       </c>
@@ -7208,7 +7205,7 @@
         <v>236.2</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>604</v>
       </c>
@@ -7216,7 +7213,7 @@
         <v>334.3</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>605</v>
       </c>
@@ -7224,18 +7221,15 @@
         <v>235.55</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>606</v>
       </c>
       <c r="B606" s="2">
         <v>235.65</v>
       </c>
-      <c r="G606" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>607</v>
       </c>
@@ -7243,7 +7237,7 @@
         <v>235.75</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>608</v>
       </c>
